--- a/相关论文汇总/论文列表.xlsx
+++ b/相关论文汇总/论文列表.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,41 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="457">
-  <si>
-    <t>北洋-脑海服务器租赁</t>
-  </si>
-  <si>
-    <t>账号密码</t>
-  </si>
-  <si>
-    <t>服务器配置</t>
-  </si>
-  <si>
-    <t>租赁周期/月</t>
-  </si>
-  <si>
-    <t>ip：106.15.46.63:22
-ssh账号： big_bao
-密码：b_1@1_d</t>
-  </si>
-  <si>
-    <t>实例规格：8核 16Gecs.e系列 V
-I/O 优化实例：I/O 优化实例
-系统盘：ESSD Entry/dev/xvda40GB模块属性
-带宽：5Mbps按固定带宽
-CPU：8核
-可用区：华东2 可用区B
-操作系统：Ubuntu 24.04 64位Linuxlinux64位
-内存：16GB
-地域：华东2（上海）
-虚拟交换机：vsw-uf6cst0qk3nqev9okvr9g
-网络类型：专有网络</t>
-  </si>
-  <si>
-    <t>400元/月
-（试用期一个月）</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="450">
   <si>
     <t>Study Name</t>
   </si>
@@ -1461,6 +1425,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>JCR  Q1</t>
     </r>
     <r>
@@ -1499,6 +1469,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>医学</t>
     </r>
     <r>
@@ -2182,7 +2158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2191,18 +2167,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2515,56 +2479,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="1" width="34.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="60.4666666666667" customWidth="1"/>
-    <col min="3" max="3" width="27" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" ht="148.5" spans="1:3">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:D216"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
@@ -2575,27 +2489,27 @@
   <sheetData>
     <row r="1" ht="23.25" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="36" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1">
         <v>2015</v>
@@ -2603,13 +2517,13 @@
     </row>
     <row r="3" ht="24" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>2015</v>
@@ -2617,13 +2531,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>2016</v>
@@ -2631,13 +2545,13 @@
     </row>
     <row r="5" ht="48" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1">
         <v>2016</v>
@@ -2645,13 +2559,13 @@
     </row>
     <row r="6" ht="48" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1">
         <v>2016</v>
@@ -2659,13 +2573,13 @@
     </row>
     <row r="7" ht="36" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1">
         <v>2016</v>
@@ -2673,13 +2587,13 @@
     </row>
     <row r="8" ht="24" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1">
         <v>2016</v>
@@ -2687,13 +2601,13 @@
     </row>
     <row r="9" ht="36" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1">
         <v>2016</v>
@@ -2701,13 +2615,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
         <v>2016</v>
@@ -2715,13 +2629,13 @@
     </row>
     <row r="11" ht="24" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1">
         <v>2017</v>
@@ -2729,13 +2643,13 @@
     </row>
     <row r="12" ht="24" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1">
         <v>2017</v>
@@ -2743,13 +2657,13 @@
     </row>
     <row r="13" ht="36" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1">
         <v>2017</v>
@@ -2757,13 +2671,13 @@
     </row>
     <row r="14" ht="36" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1">
         <v>2017</v>
@@ -2771,10 +2685,10 @@
     </row>
     <row r="15" ht="24" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1">
         <v>2017</v>
@@ -2782,13 +2696,13 @@
     </row>
     <row r="16" ht="24" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1">
         <v>2017</v>
@@ -2796,13 +2710,13 @@
     </row>
     <row r="17" ht="36" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="D17" s="1">
         <v>2017</v>
@@ -2810,10 +2724,10 @@
     </row>
     <row r="18" ht="24" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D18" s="1">
         <v>2018</v>
@@ -2821,13 +2735,13 @@
     </row>
     <row r="19" ht="24" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D19" s="1">
         <v>2018</v>
@@ -2835,13 +2749,13 @@
     </row>
     <row r="20" ht="24" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1">
         <v>2018</v>
@@ -2849,13 +2763,13 @@
     </row>
     <row r="21" ht="36" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D21" s="1">
         <v>2018</v>
@@ -2863,13 +2777,13 @@
     </row>
     <row r="22" ht="36" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D22" s="1">
         <v>2018</v>
@@ -2877,13 +2791,13 @@
     </row>
     <row r="23" ht="48" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1">
         <v>2018</v>
@@ -2891,13 +2805,13 @@
     </row>
     <row r="24" ht="36" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D24" s="1">
         <v>2018</v>
@@ -2905,13 +2819,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D25" s="1">
         <v>2018</v>
@@ -2919,13 +2833,13 @@
     </row>
     <row r="26" ht="36" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D26" s="1">
         <v>2018</v>
@@ -2933,13 +2847,13 @@
     </row>
     <row r="27" ht="36" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D27" s="1">
         <v>2018</v>
@@ -2947,13 +2861,13 @@
     </row>
     <row r="28" ht="36" spans="1:4">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D28" s="1">
         <v>2018</v>
@@ -2961,13 +2875,13 @@
     </row>
     <row r="29" ht="24" spans="1:4">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D29" s="1">
         <v>2019</v>
@@ -2975,13 +2889,13 @@
     </row>
     <row r="30" ht="36" spans="1:4">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D30" s="1">
         <v>2019</v>
@@ -2989,13 +2903,13 @@
     </row>
     <row r="31" ht="60" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D31" s="1">
         <v>2019</v>
@@ -3003,13 +2917,13 @@
     </row>
     <row r="32" ht="36" spans="1:4">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="D32" s="1">
         <v>2019</v>
@@ -3017,13 +2931,13 @@
     </row>
     <row r="33" ht="36" spans="1:4">
       <c r="A33" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D33" s="1">
         <v>2019</v>
@@ -3031,13 +2945,13 @@
     </row>
     <row r="34" ht="36" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D34" s="1">
         <v>2019</v>
@@ -3045,13 +2959,13 @@
     </row>
     <row r="35" ht="60" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D35" s="1">
         <v>2019</v>
@@ -3059,13 +2973,13 @@
     </row>
     <row r="36" ht="24" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D36" s="1">
         <v>2019</v>
@@ -3073,13 +2987,13 @@
     </row>
     <row r="37" ht="48" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D37" s="1">
         <v>2019</v>
@@ -3087,13 +3001,13 @@
     </row>
     <row r="38" ht="24" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1">
         <v>2019</v>
@@ -3101,13 +3015,13 @@
     </row>
     <row r="39" ht="24" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D39" s="1">
         <v>2019</v>
@@ -3115,13 +3029,13 @@
     </row>
     <row r="40" ht="24" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1">
         <v>2019</v>
@@ -3129,13 +3043,13 @@
     </row>
     <row r="41" ht="36" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D41" s="1">
         <v>2019</v>
@@ -3143,13 +3057,13 @@
     </row>
     <row r="42" ht="36" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D42" s="1">
         <v>2019</v>
@@ -3157,13 +3071,13 @@
     </row>
     <row r="43" ht="24" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D43" s="1">
         <v>2019</v>
@@ -3171,13 +3085,13 @@
     </row>
     <row r="44" ht="36" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D44" s="1">
         <v>2019</v>
@@ -3185,13 +3099,13 @@
     </row>
     <row r="45" ht="36" spans="1:4">
       <c r="A45" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D45" s="1">
         <v>2019</v>
@@ -3199,13 +3113,13 @@
     </row>
     <row r="46" ht="24" spans="1:4">
       <c r="A46" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D46" s="1">
         <v>2020</v>
@@ -3213,13 +3127,13 @@
     </row>
     <row r="47" ht="36" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D47" s="1">
         <v>2020</v>
@@ -3227,13 +3141,13 @@
     </row>
     <row r="48" ht="24" spans="1:4">
       <c r="A48" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D48" s="1">
         <v>2020</v>
@@ -3241,13 +3155,13 @@
     </row>
     <row r="49" ht="36" spans="1:4">
       <c r="A49" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D49" s="1">
         <v>2020</v>
@@ -3255,13 +3169,13 @@
     </row>
     <row r="50" ht="24" spans="1:4">
       <c r="A50" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D50" s="1">
         <v>2020</v>
@@ -3269,13 +3183,13 @@
     </row>
     <row r="51" ht="24" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D51" s="1">
         <v>2020</v>
@@ -3283,13 +3197,13 @@
     </row>
     <row r="52" ht="24" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D52" s="1">
         <v>2020</v>
@@ -3297,13 +3211,13 @@
     </row>
     <row r="53" ht="24" spans="1:4">
       <c r="A53" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D53" s="1">
         <v>2020</v>
@@ -3311,13 +3225,13 @@
     </row>
     <row r="54" ht="24" spans="1:4">
       <c r="A54" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D54" s="1">
         <v>2020</v>
@@ -3325,13 +3239,13 @@
     </row>
     <row r="55" ht="48" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D55" s="1">
         <v>2020</v>
@@ -3339,13 +3253,13 @@
     </row>
     <row r="56" ht="24" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D56" s="1">
         <v>2020</v>
@@ -3353,13 +3267,13 @@
     </row>
     <row r="57" ht="24" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D57" s="1">
         <v>2020</v>
@@ -3367,13 +3281,13 @@
     </row>
     <row r="58" ht="24" spans="1:4">
       <c r="A58" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D58" s="1">
         <v>2021</v>
@@ -3381,13 +3295,13 @@
     </row>
     <row r="59" ht="24" spans="1:4">
       <c r="A59" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D59" s="1">
         <v>2021</v>
@@ -3395,13 +3309,13 @@
     </row>
     <row r="60" ht="48" spans="1:4">
       <c r="A60" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D60" s="1">
         <v>2021</v>
@@ -3409,13 +3323,13 @@
     </row>
     <row r="61" ht="48" spans="1:4">
       <c r="A61" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D61" s="1">
         <v>2021</v>
@@ -3423,13 +3337,13 @@
     </row>
     <row r="62" ht="36" spans="1:4">
       <c r="A62" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D62" s="1">
         <v>2021</v>
@@ -3437,13 +3351,13 @@
     </row>
     <row r="63" ht="24" spans="1:4">
       <c r="A63" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D63" s="1">
         <v>2021</v>
@@ -3451,13 +3365,13 @@
     </row>
     <row r="64" ht="60" spans="1:4">
       <c r="A64" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D64" s="1">
         <v>2021</v>
@@ -3465,13 +3379,13 @@
     </row>
     <row r="65" ht="48" spans="1:4">
       <c r="A65" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D65" s="1">
         <v>2021</v>
@@ -3479,13 +3393,13 @@
     </row>
     <row r="66" ht="24" spans="1:4">
       <c r="A66" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D66" s="1">
         <v>2021</v>
@@ -3493,13 +3407,13 @@
     </row>
     <row r="67" ht="24" spans="1:4">
       <c r="A67" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D67" s="1">
         <v>2021</v>
@@ -3507,13 +3421,13 @@
     </row>
     <row r="68" ht="24" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D68" s="1">
         <v>2021</v>
@@ -3521,13 +3435,13 @@
     </row>
     <row r="69" ht="24" spans="1:4">
       <c r="A69" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D69" s="1">
         <v>2021</v>
@@ -3535,13 +3449,13 @@
     </row>
     <row r="70" ht="24" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D70" s="1">
         <v>2021</v>
@@ -3549,13 +3463,13 @@
     </row>
     <row r="71" ht="24" spans="1:4">
       <c r="A71" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D71" s="1">
         <v>2022</v>
@@ -3563,13 +3477,13 @@
     </row>
     <row r="72" ht="48" spans="1:4">
       <c r="A72" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D72" s="1">
         <v>2022</v>
@@ -3577,13 +3491,13 @@
     </row>
     <row r="73" ht="48" spans="1:4">
       <c r="A73" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D73" s="1">
         <v>2022</v>
@@ -3591,13 +3505,13 @@
     </row>
     <row r="74" ht="36" spans="1:4">
       <c r="A74" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D74" s="1">
         <v>2022</v>
@@ -3605,13 +3519,13 @@
     </row>
     <row r="75" ht="24" spans="1:4">
       <c r="A75" s="1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D75" s="1">
         <v>2022</v>
@@ -3619,13 +3533,13 @@
     </row>
     <row r="76" ht="24" spans="1:4">
       <c r="A76" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D76" s="1">
         <v>2022</v>
@@ -3633,13 +3547,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D77" s="1">
         <v>2022</v>
@@ -3647,13 +3561,13 @@
     </row>
     <row r="78" ht="48" spans="1:4">
       <c r="A78" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D78" s="1">
         <v>2022</v>
@@ -3661,13 +3575,13 @@
     </row>
     <row r="79" ht="48" spans="1:4">
       <c r="A79" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D79" s="1">
         <v>2022</v>
@@ -3675,13 +3589,13 @@
     </row>
     <row r="80" ht="36" spans="1:4">
       <c r="A80" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D80" s="1">
         <v>2022</v>
@@ -3689,13 +3603,13 @@
     </row>
     <row r="81" ht="48" spans="1:4">
       <c r="A81" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D81" s="1">
         <v>2022</v>
@@ -3703,13 +3617,13 @@
     </row>
     <row r="82" ht="36" spans="1:4">
       <c r="A82" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D82" s="1">
         <v>2022</v>
@@ -3717,13 +3631,13 @@
     </row>
     <row r="83" ht="24" spans="1:4">
       <c r="A83" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D83" s="1">
         <v>2022</v>
@@ -3731,13 +3645,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D84" s="1">
         <v>2022</v>
@@ -3745,13 +3659,13 @@
     </row>
     <row r="85" ht="48" spans="1:4">
       <c r="A85" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D85" s="1">
         <v>2022</v>
@@ -3759,13 +3673,13 @@
     </row>
     <row r="86" ht="24" spans="1:4">
       <c r="A86" s="1" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D86" s="1">
         <v>2022</v>
@@ -3773,13 +3687,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D87" s="1">
         <v>2022</v>
@@ -3787,13 +3701,13 @@
     </row>
     <row r="88" ht="24" spans="1:4">
       <c r="A88" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D88" s="1">
         <v>2022</v>
@@ -3801,13 +3715,13 @@
     </row>
     <row r="89" ht="24" spans="1:4">
       <c r="A89" s="1" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D89" s="1">
         <v>2022</v>
@@ -3815,13 +3729,13 @@
     </row>
     <row r="90" ht="36" spans="1:4">
       <c r="A90" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D90" s="1">
         <v>2022</v>
@@ -3829,13 +3743,13 @@
     </row>
     <row r="91" ht="24" spans="1:4">
       <c r="A91" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D91" s="1">
         <v>2022</v>
@@ -3843,13 +3757,13 @@
     </row>
     <row r="92" ht="24" spans="1:4">
       <c r="A92" s="1" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D92" s="1">
         <v>2022</v>
@@ -3857,13 +3771,13 @@
     </row>
     <row r="93" ht="24" spans="1:4">
       <c r="A93" s="1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D93" s="1">
         <v>2023</v>
@@ -3871,13 +3785,13 @@
     </row>
     <row r="94" ht="60" spans="1:4">
       <c r="A94" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D94" s="1">
         <v>2023</v>
@@ -3885,13 +3799,13 @@
     </row>
     <row r="95" ht="24" spans="1:4">
       <c r="A95" s="1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D95" s="1">
         <v>2023</v>
@@ -3899,13 +3813,13 @@
     </row>
     <row r="96" ht="36" spans="1:4">
       <c r="A96" s="1" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D96" s="1">
         <v>2023</v>
@@ -3913,13 +3827,13 @@
     </row>
     <row r="97" ht="24" spans="1:4">
       <c r="A97" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D97" s="1">
         <v>2023</v>
@@ -3927,13 +3841,13 @@
     </row>
     <row r="98" ht="24" spans="1:4">
       <c r="A98" s="1" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D98" s="1">
         <v>2023</v>
@@ -3941,13 +3855,13 @@
     </row>
     <row r="99" ht="24" spans="1:4">
       <c r="A99" s="1" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D99" s="1">
         <v>2023</v>
@@ -3955,13 +3869,13 @@
     </row>
     <row r="100" ht="36" spans="1:4">
       <c r="A100" s="1" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D100" s="1">
         <v>2023</v>
@@ -3969,13 +3883,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D101" s="1">
         <v>2023</v>
@@ -3983,13 +3897,13 @@
     </row>
     <row r="102" ht="24" spans="1:4">
       <c r="A102" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D102" s="1">
         <v>2023</v>
@@ -3997,13 +3911,13 @@
     </row>
     <row r="103" ht="36" spans="1:4">
       <c r="A103" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D103" s="1">
         <v>2023</v>
@@ -4011,13 +3925,13 @@
     </row>
     <row r="104" ht="24" spans="1:4">
       <c r="A104" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D104" s="1">
         <v>2023</v>
@@ -4025,13 +3939,13 @@
     </row>
     <row r="105" ht="24" spans="1:4">
       <c r="A105" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D105" s="1">
         <v>2023</v>
@@ -4039,13 +3953,13 @@
     </row>
     <row r="106" ht="24" spans="1:4">
       <c r="A106" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="D106" s="1">
         <v>2023</v>
@@ -4053,13 +3967,13 @@
     </row>
     <row r="107" ht="36" spans="1:4">
       <c r="A107" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D107" s="1">
         <v>2023</v>
@@ -4067,13 +3981,13 @@
     </row>
     <row r="108" ht="36" spans="1:4">
       <c r="A108" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D108" s="1">
         <v>2023</v>
@@ -4081,13 +3995,13 @@
     </row>
     <row r="109" ht="24" spans="1:4">
       <c r="A109" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D109" s="1">
         <v>2023</v>
@@ -4095,13 +4009,13 @@
     </row>
     <row r="110" ht="24" spans="1:4">
       <c r="A110" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D110" s="1">
         <v>2023</v>
@@ -4109,13 +4023,13 @@
     </row>
     <row r="111" ht="24" spans="1:4">
       <c r="A111" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D111" s="1">
         <v>2023</v>
@@ -4123,13 +4037,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D112" s="1">
         <v>2023</v>
@@ -4137,13 +4051,13 @@
     </row>
     <row r="113" ht="24" spans="1:4">
       <c r="A113" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D113" s="1">
         <v>2023</v>
@@ -4151,13 +4065,13 @@
     </row>
     <row r="114" ht="24" spans="1:4">
       <c r="A114" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D114" s="1">
         <v>2023</v>
@@ -4165,13 +4079,13 @@
     </row>
     <row r="115" ht="24" spans="1:4">
       <c r="A115" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D115" s="1">
         <v>2023</v>
@@ -4179,13 +4093,13 @@
     </row>
     <row r="116" ht="24" spans="1:4">
       <c r="A116" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D116" s="1">
         <v>2023</v>
@@ -4193,13 +4107,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="1" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="D117" s="1">
         <v>2023</v>
@@ -4207,13 +4121,13 @@
     </row>
     <row r="118" ht="36" spans="1:4">
       <c r="A118" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D118" s="1">
         <v>2023</v>
@@ -4221,13 +4135,13 @@
     </row>
     <row r="119" ht="36" spans="1:4">
       <c r="A119" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D119" s="1">
         <v>2023</v>
@@ -4235,13 +4149,13 @@
     </row>
     <row r="120" ht="48" spans="1:4">
       <c r="A120" s="1" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D120" s="1">
         <v>2023</v>
@@ -4249,13 +4163,13 @@
     </row>
     <row r="121" ht="24" spans="1:4">
       <c r="A121" s="1" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D121" s="1">
         <v>2023</v>
@@ -4263,13 +4177,13 @@
     </row>
     <row r="122" ht="24" spans="1:4">
       <c r="A122" s="1" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D122" s="1">
         <v>2023</v>
@@ -4277,13 +4191,13 @@
     </row>
     <row r="123" ht="24" spans="1:4">
       <c r="A123" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D123" s="1">
         <v>2023</v>
@@ -4291,13 +4205,13 @@
     </row>
     <row r="124" ht="24" spans="1:4">
       <c r="A124" s="1" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D124" s="1">
         <v>2023</v>
@@ -4305,13 +4219,13 @@
     </row>
     <row r="125" ht="36" spans="1:4">
       <c r="A125" s="1" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="D125" s="1">
         <v>2023</v>
@@ -4319,13 +4233,13 @@
     </row>
     <row r="126" ht="36" spans="1:4">
       <c r="A126" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D126" s="1">
         <v>2024</v>
@@ -4333,13 +4247,13 @@
     </row>
     <row r="127" ht="36" spans="1:4">
       <c r="A127" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D127" s="1">
         <v>2024</v>
@@ -4347,13 +4261,13 @@
     </row>
     <row r="128" ht="48" spans="1:4">
       <c r="A128" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D128" s="1">
         <v>2024</v>
@@ -4361,13 +4275,13 @@
     </row>
     <row r="129" ht="24" spans="1:4">
       <c r="A129" s="1" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D129" s="1">
         <v>2024</v>
@@ -4375,13 +4289,13 @@
     </row>
     <row r="130" ht="24" spans="1:4">
       <c r="A130" s="1" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D130" s="1">
         <v>2024</v>
@@ -4389,13 +4303,13 @@
     </row>
     <row r="131" ht="24" spans="1:4">
       <c r="A131" s="1" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D131" s="1">
         <v>2024</v>
@@ -4403,13 +4317,13 @@
     </row>
     <row r="132" ht="24" spans="1:4">
       <c r="A132" s="1" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D132" s="1">
         <v>2024</v>
@@ -4417,13 +4331,13 @@
     </row>
     <row r="133" ht="36" spans="1:4">
       <c r="A133" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D133" s="1">
         <v>2024</v>
@@ -4431,13 +4345,13 @@
     </row>
     <row r="134" ht="24" spans="1:4">
       <c r="A134" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D134" s="1">
         <v>2024</v>
@@ -4445,13 +4359,13 @@
     </row>
     <row r="135" ht="24" spans="1:4">
       <c r="A135" s="1" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D135" s="1">
         <v>2024</v>
@@ -4459,13 +4373,13 @@
     </row>
     <row r="136" ht="24" spans="1:4">
       <c r="A136" s="1" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D136" s="1">
         <v>2024</v>
@@ -4473,13 +4387,13 @@
     </row>
     <row r="137" ht="36" spans="1:4">
       <c r="A137" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D137" s="1">
         <v>2024</v>
@@ -4487,13 +4401,13 @@
     </row>
     <row r="138" ht="36" spans="1:4">
       <c r="A138" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D138" s="1">
         <v>2024</v>
@@ -4501,10 +4415,10 @@
     </row>
     <row r="139" ht="24" spans="1:4">
       <c r="A139" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D139" s="1">
         <v>2025</v>
@@ -4512,10 +4426,10 @@
     </row>
     <row r="140" ht="24" spans="1:4">
       <c r="A140" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D140" s="1">
         <v>2025</v>
@@ -4523,10 +4437,10 @@
     </row>
     <row r="141" ht="24" spans="1:4">
       <c r="A141" s="1" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D141" s="1">
         <v>2025</v>
@@ -4534,10 +4448,10 @@
     </row>
     <row r="142" ht="24" spans="1:4">
       <c r="A142" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D142" s="1">
         <v>2025</v>
@@ -4545,10 +4459,10 @@
     </row>
     <row r="143" ht="24" spans="1:4">
       <c r="A143" s="1" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D143" s="1">
         <v>2025</v>
@@ -4556,10 +4470,10 @@
     </row>
     <row r="144" ht="24" spans="1:4">
       <c r="A144" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D144" s="1">
         <v>2025</v>
@@ -4567,10 +4481,10 @@
     </row>
     <row r="145" ht="24" spans="1:4">
       <c r="A145" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D145" s="1">
         <v>2025</v>
@@ -4578,10 +4492,10 @@
     </row>
     <row r="146" ht="36" spans="1:4">
       <c r="A146" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D146" s="1">
         <v>2025</v>
@@ -4589,10 +4503,10 @@
     </row>
     <row r="147" ht="36" spans="1:4">
       <c r="A147" s="1" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D147" s="1">
         <v>2025</v>
@@ -4600,10 +4514,10 @@
     </row>
     <row r="148" ht="24" spans="1:4">
       <c r="A148" s="1" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="D148" s="1">
         <v>2025</v>
@@ -4611,10 +4525,10 @@
     </row>
     <row r="149" ht="24" spans="1:4">
       <c r="A149" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D149" s="1">
         <v>2025</v>
@@ -4622,13 +4536,13 @@
     </row>
     <row r="150" ht="24" spans="1:4">
       <c r="A150" s="1" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D150" s="1">
         <v>2025</v>
@@ -4636,10 +4550,10 @@
     </row>
     <row r="151" ht="24" spans="1:4">
       <c r="A151" s="1" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D151" s="1">
         <v>2025</v>
@@ -4647,13 +4561,13 @@
     </row>
     <row r="152" ht="24" spans="1:4">
       <c r="A152" s="1" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D152" s="1">
         <v>2025</v>
@@ -4661,10 +4575,10 @@
     </row>
     <row r="153" ht="24" spans="1:4">
       <c r="A153" s="1" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D153" s="1">
         <v>2025</v>
@@ -4672,13 +4586,13 @@
     </row>
     <row r="154" ht="24" spans="1:4">
       <c r="A154" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="D154" s="1">
         <v>2025</v>
@@ -4686,13 +4600,13 @@
     </row>
     <row r="155" ht="48" spans="1:4">
       <c r="A155" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D155" s="1">
         <v>2025</v>
@@ -4700,13 +4614,13 @@
     </row>
     <row r="156" ht="24" spans="1:4">
       <c r="A156" s="1" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D156" s="1">
         <v>2025</v>
@@ -4714,13 +4628,13 @@
     </row>
     <row r="157" ht="24" spans="1:4">
       <c r="A157" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D157" s="1">
         <v>2025</v>
@@ -4728,13 +4642,13 @@
     </row>
     <row r="158" ht="36" spans="1:4">
       <c r="A158" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D158" s="1">
         <v>2025</v>
@@ -4742,13 +4656,13 @@
     </row>
     <row r="159" ht="24" spans="1:4">
       <c r="A159" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="D159" s="1">
         <v>2025</v>
@@ -4756,10 +4670,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D160" s="1">
         <v>2025</v>
@@ -4767,10 +4681,10 @@
     </row>
     <row r="161" ht="36" spans="1:4">
       <c r="A161" s="1" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="D161" s="1">
         <v>2025</v>
@@ -4778,13 +4692,13 @@
     </row>
     <row r="162" ht="24" spans="1:4">
       <c r="A162" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D162" s="1">
         <v>2025</v>
@@ -4792,10 +4706,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="1" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D163" s="1">
         <v>2025</v>
@@ -4803,10 +4717,10 @@
     </row>
     <row r="164" ht="24" spans="1:4">
       <c r="A164" s="1" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D164" s="1">
         <v>2025</v>
@@ -4814,13 +4728,13 @@
     </row>
     <row r="165" ht="36" spans="1:4">
       <c r="A165" s="1" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D165" s="1">
         <v>2025</v>
@@ -4828,10 +4742,10 @@
     </row>
     <row r="166" ht="36" spans="1:4">
       <c r="A166" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D166" s="1">
         <v>2025</v>
@@ -4839,13 +4753,13 @@
     </row>
     <row r="167" ht="36" spans="1:4">
       <c r="A167" s="1" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D167" s="1">
         <v>2025</v>
@@ -4853,10 +4767,10 @@
     </row>
     <row r="168" ht="24" spans="1:4">
       <c r="A168" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D168" s="1">
         <v>2025</v>
@@ -4864,13 +4778,13 @@
     </row>
     <row r="169" ht="24" spans="1:4">
       <c r="A169" s="1" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D169" s="1">
         <v>2025</v>
@@ -4878,13 +4792,13 @@
     </row>
     <row r="170" ht="24" spans="1:4">
       <c r="A170" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D170" s="1">
         <v>2025</v>
@@ -4892,13 +4806,13 @@
     </row>
     <row r="171" ht="24" spans="1:4">
       <c r="A171" s="1" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D171" s="1">
         <v>2025</v>
@@ -4906,13 +4820,13 @@
     </row>
     <row r="172" ht="24" spans="1:4">
       <c r="A172" s="1" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D172" s="1">
         <v>2025</v>
@@ -4920,13 +4834,13 @@
     </row>
     <row r="173" ht="36" spans="1:4">
       <c r="A173" s="1" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D173" s="1">
         <v>2025</v>
@@ -4934,10 +4848,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="1" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D174" s="1">
         <v>2025</v>
@@ -4945,13 +4859,13 @@
     </row>
     <row r="175" ht="36" spans="1:4">
       <c r="A175" s="1" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D175" s="1">
         <v>2025</v>
@@ -4959,13 +4873,13 @@
     </row>
     <row r="176" ht="24" spans="1:4">
       <c r="A176" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D176" s="1">
         <v>2025</v>
@@ -4973,13 +4887,13 @@
     </row>
     <row r="177" ht="24" spans="1:4">
       <c r="A177" s="1" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D177" s="1">
         <v>2025</v>
@@ -4987,13 +4901,13 @@
     </row>
     <row r="178" ht="24" spans="1:4">
       <c r="A178" s="1" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D178" s="1">
         <v>2025</v>
@@ -5001,10 +4915,10 @@
     </row>
     <row r="179" ht="24" spans="1:4">
       <c r="A179" s="1" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D179" s="1">
         <v>2025</v>
@@ -5012,10 +4926,10 @@
     </row>
     <row r="180" ht="24" spans="1:4">
       <c r="A180" s="1" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D180" s="1">
         <v>2025</v>
@@ -5023,13 +4937,13 @@
     </row>
     <row r="181" ht="24" spans="1:4">
       <c r="A181" s="1" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D181" s="1">
         <v>2025</v>
@@ -5037,13 +4951,13 @@
     </row>
     <row r="182" ht="24" spans="1:4">
       <c r="A182" s="1" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D182" s="1">
         <v>2025</v>
@@ -5051,10 +4965,10 @@
     </row>
     <row r="183" ht="24" spans="1:4">
       <c r="A183" s="1" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D183" s="1">
         <v>2025</v>
@@ -5062,13 +4976,13 @@
     </row>
     <row r="184" ht="36" spans="1:4">
       <c r="A184" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D184" s="1">
         <v>2025</v>
@@ -5076,35 +4990,35 @@
     </row>
     <row r="185" ht="24" spans="1:4">
       <c r="A185" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186" ht="24" spans="1:4">
       <c r="A186" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187" ht="24" spans="1:4">
       <c r="A187" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D187" s="1">
         <v>2026</v>
@@ -5112,13 +5026,13 @@
     </row>
     <row r="188" ht="24" spans="1:4">
       <c r="A188" s="1" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D188" s="1">
         <v>2026</v>
@@ -5126,13 +5040,13 @@
     </row>
     <row r="189" ht="24" spans="1:4">
       <c r="A189" s="1" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D189" s="1">
         <v>2026</v>
@@ -5140,13 +5054,13 @@
     </row>
     <row r="190" ht="24" spans="1:4">
       <c r="A190" s="1" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D190" s="1">
         <v>2026</v>
@@ -5154,13 +5068,13 @@
     </row>
     <row r="191" ht="24" spans="1:4">
       <c r="A191" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D191" s="1">
         <v>2026</v>
@@ -5168,13 +5082,13 @@
     </row>
     <row r="192" ht="24" spans="1:4">
       <c r="A192" s="1" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D192" s="1">
         <v>2026</v>
@@ -5182,13 +5096,13 @@
     </row>
     <row r="193" ht="24" spans="1:4">
       <c r="A193" s="1" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D193" s="1">
         <v>2026</v>
@@ -5196,13 +5110,13 @@
     </row>
     <row r="194" ht="24" spans="1:4">
       <c r="A194" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D194" s="1">
         <v>2026</v>
@@ -5210,13 +5124,13 @@
     </row>
     <row r="195" ht="25" customHeight="1" spans="1:4">
       <c r="A195" s="1" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D195" s="1">
         <v>2026</v>
@@ -5224,13 +5138,13 @@
     </row>
     <row r="196" ht="24" spans="1:4">
       <c r="A196" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D196" s="1">
         <v>2026</v>
@@ -5238,13 +5152,13 @@
     </row>
     <row r="197" ht="36" spans="1:4">
       <c r="A197" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D197" s="1">
         <v>2026</v>
@@ -5252,13 +5166,13 @@
     </row>
     <row r="198" ht="48" spans="1:4">
       <c r="A198" s="1" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D198" s="1">
         <v>2026</v>
@@ -5266,13 +5180,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D199" s="1">
         <v>2026</v>
@@ -5280,13 +5194,13 @@
     </row>
     <row r="200" ht="24" spans="1:4">
       <c r="A200" s="1" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D200" s="1">
         <v>2026</v>
@@ -5294,13 +5208,13 @@
     </row>
     <row r="201" ht="24" spans="1:4">
       <c r="A201" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D201" s="1">
         <v>2026</v>
@@ -5308,13 +5222,13 @@
     </row>
     <row r="202" ht="24" spans="1:4">
       <c r="A202" s="1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D202" s="1">
         <v>2026</v>
@@ -5322,13 +5236,13 @@
     </row>
     <row r="203" ht="24" spans="1:4">
       <c r="A203" s="1" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D203" s="1">
         <v>2026</v>
@@ -5336,13 +5250,13 @@
     </row>
     <row r="204" ht="48" spans="1:4">
       <c r="A204" s="1" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D204" s="1">
         <v>2026</v>
@@ -5350,13 +5264,13 @@
     </row>
     <row r="205" ht="24" spans="1:4">
       <c r="A205" s="1" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D205" s="1">
         <v>2026</v>
@@ -5364,13 +5278,13 @@
     </row>
     <row r="206" ht="36" spans="1:4">
       <c r="A206" s="1" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D206" s="1">
         <v>2026</v>
@@ -5378,13 +5292,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D207" s="1">
         <v>2026</v>
@@ -5392,13 +5306,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D208" s="1">
         <v>2026</v>
@@ -5406,13 +5320,13 @@
     </row>
     <row r="209" ht="36" spans="1:4">
       <c r="A209" s="1" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="D209" s="1">
         <v>2026</v>
@@ -5420,13 +5334,13 @@
     </row>
     <row r="210" ht="24" spans="1:4">
       <c r="A210" s="1" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D210" s="1">
         <v>2026</v>
@@ -5434,13 +5348,13 @@
     </row>
     <row r="211" ht="24" spans="1:4">
       <c r="A211" s="1" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="D211" s="1">
         <v>2026</v>
@@ -5448,13 +5362,13 @@
     </row>
     <row r="212" ht="24" spans="1:4">
       <c r="A212" s="1" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="D212" s="1">
         <v>2026</v>
@@ -5462,13 +5376,13 @@
     </row>
     <row r="213" ht="24" spans="1:4">
       <c r="A213" s="1" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D213" s="1">
         <v>2026</v>
@@ -5476,13 +5390,13 @@
     </row>
     <row r="214" ht="36" spans="1:4">
       <c r="A214" s="1" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D214" s="1">
         <v>2026</v>
@@ -5490,13 +5404,13 @@
     </row>
     <row r="215" ht="24" spans="1:4">
       <c r="A215" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D215" s="1">
         <v>2026</v>
@@ -5504,13 +5418,13 @@
     </row>
     <row r="216" ht="24" spans="1:4">
       <c r="A216" s="1" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D216" s="1">
         <v>2026</v>
@@ -5524,16 +5438,4 @@
   <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>